--- a/20260804_権限設定_検証資料.xlsx
+++ b/20260804_権限設定_検証資料.xlsx
@@ -2342,7 +2342,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="58" customWidth="1" min="5" max="5"/>
     <col width="58" customWidth="1" min="6" max="6"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>dataset/08 のとおり作成（経理担当・人事担当・エリア長・バイトリーダー・閲覧のみ・スタッフ）。エリア長は既定テンプレに無いため店長をベースに作る。保存後に再度開いて設定が再現するか確認</t>
+          <t>dataset/08 のとおり作成（経理担当・人事担当・エリア長・バイトリーダー・閲覧のみ・スタッフ）。**エリア長は既定テンプレートに無い＝店長を雛形に選び、権限名を『検証_エリア長』に変えて作る**（顧客が実際に行うカスタマイズの再現）。保存後に再度開いて設定が再現するか確認</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>エリア長から売上分析をオフにして保存→US-03のセッションで画面遷移→確認後に元へ戻す</t>
+          <t>検証_エリア長（店長ベースで作成）から売上分析をオフにして保存→US-03のセッションで画面遷移→確認後に元へ戻す</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>US-03 エリア長</t>
+          <t>US-03 エリア長（店長ベースのカスタマイズ例）</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>US-03 エリア長でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
+          <t>US-03 検証_エリア長でログインし、許可画面を順に開く→次に不許可画面をメニュー確認し直URLでも開く</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>US-07（エリア長）の割当編集で経理担当に付け替え、行の表示を確認してから保存→US-07でログイン。次に一括割当で同じ人を含める</t>
+          <t>US-07（検証_エリア長）の割当編集で経理担当に付け替え、行の表示を確認してから保存→US-07でログイン。次に一括割当で同じ人を含める</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>エリア長（店舗）で一括割当を開く→「すべて表示」</t>
+          <t>検証_エリア長（店舗）で一括割当を開く→「すべて表示」</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>スタッフ・エリア長・経理の指標一覧を開き、店舗／会社タブのON件数を数える。任意の指標をON/OFF</t>
+          <t>スタッフ・検証_エリア長・経理の指標一覧を開き、店舗／会社タブのON件数を数える。任意の指標をON/OFF</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>スタッフ=店舗17/会社0、エリア長=店舗36/会社8、経理=店舗36/会社25。切替は即時反映</t>
+          <t>スタッフ=店舗17/会社0、エリア長（店長ベース）=店舗36/会社8、経理=店舗36/会社25。切替は即時反映</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>SC-01経理／SC-02人事／SC-03エリア長／SC-04バイトL／SC-05閲覧のみ／SC-06スタッフ を ◯作れる／△粒度不足／×作れない で記録。**本検証の結論**</t>
+          <t>SC-01経理／SC-02人事／SC-03エリア長（カスタマイズ例／本機能の価値の中心）／SC-04バイトL／SC-05閲覧のみ／SC-06スタッフ を ◯作れる／△粒度不足／×作れない で記録。**本検証の結論**</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>SC-03 エリア長。T-24の主役</t>
+          <t>SC-03 エリア長（店長ベースのカスタマイズ例）。担当外店舗の検証で主役</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>検証_エリア長 → 検証_経理担当</t>
+          <t>検証_エリア長（店長ベース）→ 検証_経理担当</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>⑧ 権限設定値（権限6件 × 画面。S-04でそのまま入力。エリア長は店長ベースのカスタマイズ例）</t>
+          <t>⑧ 権限設定値（権限6件 × 画面。S-04でそのまま入力。エリア長は既定テンプレに無く店長ベースで作るカスタマイズ例）</t>
         </is>
       </c>
       <c r="B53" s="9" t="n"/>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>店長（shop_manager移植プリセット）</t>
+          <t>店長（既定テンプレ）※カスタマイズ例</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">

--- a/20260804_権限設定_検証資料.xlsx
+++ b/20260804_権限設定_検証資料.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証データセット" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$2:$N$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'受入条件表'!$A$2:$N$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'検証プラン'!$A$2:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,15 +504,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>リリース可否の判断基準（31条件）。「どの条件を満たせばリリースしてよいか」を決める表。黄色は記入欄。</t>
+          <t>リリース可否の判断基準（33条件：必須28／次段階5）。必須を全部満たしてもMVP達成ではない ── 顧客要望4つのうちP1で満たせるのは1つ（AC-10/11）で、残り3つはAC-23/24/25＝次段階。黄色は記入欄。</t>
         </is>
       </c>
     </row>
@@ -1796,17 +1796,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>顧客が求める権限を意図どおり作れる</t>
+          <t>顧客が求める権限を意図どおり作れる（画面単位で表現できる範囲）</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>6シナリオの判定を確定（◯/△/×の件数）</t>
+          <t>SC-01経理／SC-02人事／SC-04バイトL／SC-06スタッフ の4件で ×（作れない）＝0件。△は過不足の内容を必ず記録</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>SC-01〜06の総合判定</t>
+          <t>T-22 の6シナリオ判定のうち、画面単位で表現できる4件を対象に判定</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2338,8 +2338,120 @@
       <c r="M33" s="4" t="inlineStr"/>
       <c r="N33" s="4" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>AC-32</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>P2/P3</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>意図</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>データ範囲・操作を要する権限が作れる</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>SC-03エリア長／SC-05閲覧のみ の2件が ◯（作れる）</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>T-22の該当2件を判定。P1時点では×が想定され、それがP2/P3を前倒しする根拠になる</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>T-22.png</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>T-22 T-23</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>§1.2 顧客要望 / §8-6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>次段階</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr"/>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>AC-33</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>導入</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>導入時に権限をまとめて用意でき、やり直せる</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>権限テンプレートが適用でき権限一覧に登録される。下書きの一時保存で復元、破棄で初期化できる</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>T-04 を実施</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>T-04.png</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>T-04</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>§5.6 F-01 F-02 F-25</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N33"/>
+  <autoFilter ref="A2:N35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2358,7 +2470,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="58" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -2368,7 +2480,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（29ケース）。上から順に実施する。S-01〜S-06が準備、T-01以降が検証。黄色は記入欄。</t>
+          <t>確かめる手順（29ケース）。上から順に実施。S-01〜S-06が準備、T-01以降が検証。黄色は記入欄。</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2970,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>F-01 F-02 F-25</t>
+          <t>AC-33／F-01 F-02 F-25</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
@@ -3640,7 +3752,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>SC-01経理／SC-02人事／SC-03エリア長（カスタマイズ例／本機能の価値の中心）／SC-04バイトL／SC-05閲覧のみ／SC-06スタッフ を ◯作れる／△粒度不足／×作れない で記録。**本検証の結論**</t>
+          <t>6件を ◯作れる／△粒度不足／×作れない で記録。**【必須ライン】画面単位で表現できる SC-01経理・SC-02人事・SC-04バイトL・SC-06スタッフ の4件で ×＝0件**（AC-22）。SC-03エリア長・SC-05閲覧のみ はデータ範囲・操作を要するため P1 では×が想定され、それが P2/P3 を前倒しする根拠になる（AC-32）</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -3650,7 +3762,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-22 AC-32</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr"/>

--- a/20260804_権限設定_検証資料.xlsx
+++ b/20260804_権限設定_検証資料.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>リリース可否の判断基準（33条件：必須28／次段階5）。必須を全部満たしてもMVP達成ではない ── 顧客要望4つのうちP1で満たせるのは1つ（AC-10/11）で、残り3つはAC-23/24/25＝次段階。黄色は記入欄。</t>
+          <t>リリース可否の判断基準。必須を全部満たしてもMVP達成ではない ── 顧客要望4つのうちP1で満たせるのは1つ（AC-10/11）、残り3つはAC-23/24/25＝次段階。黄色は記入欄。</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確かめる手順（29ケース）。上から順に実施。S-01〜S-06が準備、T-01以降が検証。黄色は記入欄。</t>
+          <t>確かめる手順。上から順に実施する。S-01〜S-06が準備、T-01以降が検証。黄色は記入欄。</t>
         </is>
       </c>
     </row>
